--- a/data/metadata.xlsx
+++ b/data/metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF962F5B-6B80-4943-B1A5-CDDF94F8ECD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837E5E5B-DFCA-472C-9CAA-68BA9599DC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6252" uniqueCount="1276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6711" uniqueCount="1410">
   <si>
     <t>ASSET_CLASS</t>
   </si>
@@ -3760,39 +3760,6 @@
     <t>CRSPMC</t>
   </si>
   <si>
-    <t>CRSPEN</t>
-  </si>
-  <si>
-    <t>CRSPMT</t>
-  </si>
-  <si>
-    <t>CRSPID</t>
-  </si>
-  <si>
-    <t>CRSPCD</t>
-  </si>
-  <si>
-    <t>CRSPCS</t>
-  </si>
-  <si>
-    <t>CRSPHC</t>
-  </si>
-  <si>
-    <t>CRSPFN</t>
-  </si>
-  <si>
-    <t>CRSPIT</t>
-  </si>
-  <si>
-    <t>CRSPTE</t>
-  </si>
-  <si>
-    <t>CRSPUT</t>
-  </si>
-  <si>
-    <t>CRSPRE</t>
-  </si>
-  <si>
     <t>CRSPME1</t>
   </si>
   <si>
@@ -3872,6 +3839,441 @@
   </si>
   <si>
     <t>^GSPC</t>
+  </si>
+  <si>
+    <t>TSE</t>
+  </si>
+  <si>
+    <t>Broad Market</t>
+  </si>
+  <si>
+    <t>TOPIX</t>
+  </si>
+  <si>
+    <t>TOPIX100</t>
+  </si>
+  <si>
+    <t>TOPIX 100</t>
+  </si>
+  <si>
+    <t>TOPIX500</t>
+  </si>
+  <si>
+    <t>TOPIX 500</t>
+  </si>
+  <si>
+    <t>TOPIX1000</t>
+  </si>
+  <si>
+    <t>TOPIX 1000</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>T17B</t>
+  </si>
+  <si>
+    <t>TOPIX-17 BANKS</t>
+  </si>
+  <si>
+    <t>Food Products</t>
+  </si>
+  <si>
+    <t>T17FD</t>
+  </si>
+  <si>
+    <t>TOPIX-17 FOODS</t>
+  </si>
+  <si>
+    <t>Retail Trade</t>
+  </si>
+  <si>
+    <t>T17RT</t>
+  </si>
+  <si>
+    <t>TOPIX-17 RETAIL TRADE</t>
+  </si>
+  <si>
+    <t>Machinery</t>
+  </si>
+  <si>
+    <t>T17M</t>
+  </si>
+  <si>
+    <t>TOPIX-17 MACHINERY</t>
+  </si>
+  <si>
+    <t>T17RE</t>
+  </si>
+  <si>
+    <t>TOPIX-17 REAL ESTATE</t>
+  </si>
+  <si>
+    <t>Energy Resources</t>
+  </si>
+  <si>
+    <t>T17ER</t>
+  </si>
+  <si>
+    <t>TOPIX-17 ENERGY RESOURCES</t>
+  </si>
+  <si>
+    <t>Diversified Financials &amp; Insurance</t>
+  </si>
+  <si>
+    <t>T17FIN</t>
+  </si>
+  <si>
+    <t>TOPIX-17 FINANCIALS (EX BANKS)</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>T17PHR</t>
+  </si>
+  <si>
+    <t>TOPIX-17 PHARMACEUTICAL</t>
+  </si>
+  <si>
+    <t>Electric Power &amp; Gas</t>
+  </si>
+  <si>
+    <t>T17EPG</t>
+  </si>
+  <si>
+    <t>TOPIX-17 ELECTRIC POWER &amp; GAS</t>
+  </si>
+  <si>
+    <t>IT, Communication &amp; Services</t>
+  </si>
+  <si>
+    <t>T17ISO</t>
+  </si>
+  <si>
+    <t>TOPIX-17 IT &amp; SERVICES, OTHERS</t>
+  </si>
+  <si>
+    <t>Steel &amp; Nonferrous Metals</t>
+  </si>
+  <si>
+    <t>T17SNM</t>
+  </si>
+  <si>
+    <t>TOPIX-17 STEEL &amp; NONFERROUS METALS</t>
+  </si>
+  <si>
+    <t>Raw Materials &amp; Chemicals</t>
+  </si>
+  <si>
+    <t>T17RMC</t>
+  </si>
+  <si>
+    <t>TOPIX-17 RAW MATERIALS &amp; CHEMICALS</t>
+  </si>
+  <si>
+    <t>Construction &amp; Materials</t>
+  </si>
+  <si>
+    <t>T17CM</t>
+  </si>
+  <si>
+    <t>TOPIX-17 CONSTRUCTION &amp; MATERIALS</t>
+  </si>
+  <si>
+    <t>Transportation &amp; Logistics</t>
+  </si>
+  <si>
+    <t>T17TL</t>
+  </si>
+  <si>
+    <t>TOPIX-17 TRANSPORTATION &amp; LOGISTICS</t>
+  </si>
+  <si>
+    <t>Commercial &amp; Wholesale Trade</t>
+  </si>
+  <si>
+    <t>T17CWT</t>
+  </si>
+  <si>
+    <t>TOPIX-17 COMMERCIAL &amp; WHOLESALE TRADE</t>
+  </si>
+  <si>
+    <t>Automobiles &amp; Transportation Equipment</t>
+  </si>
+  <si>
+    <t>T17ATE</t>
+  </si>
+  <si>
+    <t>TOPIX-17 AUTOMOBILES &amp; TRANSPORTATION EQUIPMENT</t>
+  </si>
+  <si>
+    <t>Electric Appliances &amp; Precision Instruments</t>
+  </si>
+  <si>
+    <t>T17EAPI</t>
+  </si>
+  <si>
+    <t>TOPIX-17 ELECTRIC APPLIANCES &amp; PRECISION INSTRUMENTS</t>
+  </si>
+  <si>
+    <t>Tokyo Stock Price Index</t>
+  </si>
+  <si>
+    <t>KOSPI지수</t>
+  </si>
+  <si>
+    <t>KRX300지수</t>
+  </si>
+  <si>
+    <t>KOSPI200 지수</t>
+  </si>
+  <si>
+    <t>KOSDAQ150 지수</t>
+  </si>
+  <si>
+    <t>KOSDAQ 종합지수</t>
+  </si>
+  <si>
+    <t>KRX 자동차지수</t>
+  </si>
+  <si>
+    <t>KRX 반도체지수</t>
+  </si>
+  <si>
+    <t>KRX 헬스케어지수</t>
+  </si>
+  <si>
+    <t>KRX 금융지수</t>
+  </si>
+  <si>
+    <t>KRX 에너지화학지수</t>
+  </si>
+  <si>
+    <t>KRX 철강지수</t>
+  </si>
+  <si>
+    <t>KRX 미디어통신지수</t>
+  </si>
+  <si>
+    <t>KRX 건설지수</t>
+  </si>
+  <si>
+    <t>KRX 증권지수</t>
+  </si>
+  <si>
+    <t>KRX 기계장비지수</t>
+  </si>
+  <si>
+    <t>KRX 보험지수</t>
+  </si>
+  <si>
+    <t>KRX 교통지수</t>
+  </si>
+  <si>
+    <t>KRX 경기소비재지수</t>
+  </si>
+  <si>
+    <t>KRX 필수소비재지수</t>
+  </si>
+  <si>
+    <t>KRX 미디어&amp;엔터테인먼트지수</t>
+  </si>
+  <si>
+    <t>KRX 정보통신지수</t>
+  </si>
+  <si>
+    <t>KRX 유틸리티지수</t>
+  </si>
+  <si>
+    <t>Shanghai Composite Index</t>
+  </si>
+  <si>
+    <t>SZSE</t>
+  </si>
+  <si>
+    <t>Shenzhen Component Index</t>
+  </si>
+  <si>
+    <t>ChiNext Index</t>
+  </si>
+  <si>
+    <t>HSI</t>
+  </si>
+  <si>
+    <t>Hong Kong</t>
+  </si>
+  <si>
+    <t>Hang Seng Index</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>HSTECH</t>
+  </si>
+  <si>
+    <t>Hang Seng TECH Index</t>
+  </si>
+  <si>
+    <t>CSI 300 Index</t>
+  </si>
+  <si>
+    <t>CSI 300 Energy Index</t>
+  </si>
+  <si>
+    <t>CSI 300 Materials Index</t>
+  </si>
+  <si>
+    <t>CSI 300 Industrials Index</t>
+  </si>
+  <si>
+    <t>CSI 300 Consumer Discretionary Index</t>
+  </si>
+  <si>
+    <t>CSI 300 Consumer Staples Index</t>
+  </si>
+  <si>
+    <t>CSI 300 Health Care Index</t>
+  </si>
+  <si>
+    <t>CSI 300 Financials Index</t>
+  </si>
+  <si>
+    <t>CSI 300 Information Technology Index</t>
+  </si>
+  <si>
+    <t>CSI 300 Telecommunication Services Index</t>
+  </si>
+  <si>
+    <t>CSI 300 Utilities Index</t>
+  </si>
+  <si>
+    <t>CSI 300 Real Estate Index</t>
+  </si>
+  <si>
+    <t>SSEC</t>
+  </si>
+  <si>
+    <t>CHINEXT</t>
+  </si>
+  <si>
+    <t>CSI300</t>
+  </si>
+  <si>
+    <t>CSI30010</t>
+  </si>
+  <si>
+    <t>CSI30015</t>
+  </si>
+  <si>
+    <t>CSI30020</t>
+  </si>
+  <si>
+    <t>CSI30025</t>
+  </si>
+  <si>
+    <t>CSI30030</t>
+  </si>
+  <si>
+    <t>CSI30035</t>
+  </si>
+  <si>
+    <t>CSI30040</t>
+  </si>
+  <si>
+    <t>CSI30045</t>
+  </si>
+  <si>
+    <t>CSI30050</t>
+  </si>
+  <si>
+    <t>CSI30055</t>
+  </si>
+  <si>
+    <t>CSI30060</t>
+  </si>
+  <si>
+    <t>000001</t>
+  </si>
+  <si>
+    <t>399001</t>
+  </si>
+  <si>
+    <t>399006</t>
+  </si>
+  <si>
+    <t>000300</t>
+  </si>
+  <si>
+    <t>000908</t>
+  </si>
+  <si>
+    <t>000909</t>
+  </si>
+  <si>
+    <t>000910</t>
+  </si>
+  <si>
+    <t>000911</t>
+  </si>
+  <si>
+    <t>000912</t>
+  </si>
+  <si>
+    <t>000913</t>
+  </si>
+  <si>
+    <t>000914</t>
+  </si>
+  <si>
+    <t>000915</t>
+  </si>
+  <si>
+    <t>000916</t>
+  </si>
+  <si>
+    <t>000917</t>
+  </si>
+  <si>
+    <t>000952</t>
+  </si>
+  <si>
+    <t>CRSP10</t>
+  </si>
+  <si>
+    <t>CRSP15</t>
+  </si>
+  <si>
+    <t>CRSP20</t>
+  </si>
+  <si>
+    <t>CRSP25</t>
+  </si>
+  <si>
+    <t>CRSP30</t>
+  </si>
+  <si>
+    <t>CRSP35</t>
+  </si>
+  <si>
+    <t>CRSP40</t>
+  </si>
+  <si>
+    <t>CRSP45</t>
+  </si>
+  <si>
+    <t>CRSP50</t>
+  </si>
+  <si>
+    <t>CRSP55</t>
+  </si>
+  <si>
+    <t>CRSP60</t>
+  </si>
+  <si>
+    <t>https://www.memorymarket.com/price/ems/100264</t>
   </si>
 </sst>
 </file>
@@ -3927,13 +4329,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4214,7 +4618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O607"/>
+  <dimension ref="A1:O645"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -4222,11 +4626,12 @@
     <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.21875" customWidth="1"/>
     <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.21875" customWidth="1"/>
     <col min="10" max="10" width="40.5546875" customWidth="1"/>
-    <col min="11" max="13" width="12.88671875" customWidth="1"/>
+    <col min="11" max="11" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.88671875" customWidth="1"/>
     <col min="14" max="14" width="16.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4249,7 +4654,7 @@
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -4293,7 +4698,7 @@
       <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="s">
@@ -4325,7 +4730,7 @@
       <c r="F3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I3" t="s">
@@ -4357,7 +4762,7 @@
       <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="I4" t="s">
@@ -4389,7 +4794,7 @@
       <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I5" t="s">
@@ -4421,7 +4826,7 @@
       <c r="F6" t="s">
         <v>23</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="5" t="s">
         <v>23</v>
       </c>
       <c r="I6" t="s">
@@ -4453,7 +4858,7 @@
       <c r="F7" t="s">
         <v>16</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H7" t="s">
@@ -5569,7 +5974,7 @@
       <c r="F61" t="s">
         <v>102</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G61" s="5" t="s">
         <v>102</v>
       </c>
       <c r="H61" t="s">
@@ -5601,7 +6006,7 @@
       <c r="F62" t="s">
         <v>103</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G62" s="5" t="s">
         <v>103</v>
       </c>
       <c r="H62" t="s">
@@ -5633,7 +6038,7 @@
       <c r="F63" t="s">
         <v>104</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G63" s="5" t="s">
         <v>104</v>
       </c>
       <c r="H63" t="s">
@@ -5665,7 +6070,7 @@
       <c r="F64" t="s">
         <v>105</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G64" s="5" t="s">
         <v>105</v>
       </c>
       <c r="H64" t="s">
@@ -5697,7 +6102,7 @@
       <c r="F65" t="s">
         <v>106</v>
       </c>
-      <c r="G65" t="s">
+      <c r="G65" s="5" t="s">
         <v>106</v>
       </c>
       <c r="H65" t="s">
@@ -5729,7 +6134,7 @@
       <c r="F66" t="s">
         <v>107</v>
       </c>
-      <c r="G66" t="s">
+      <c r="G66" s="5" t="s">
         <v>107</v>
       </c>
       <c r="H66" t="s">
@@ -5761,7 +6166,7 @@
       <c r="F67" t="s">
         <v>108</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G67" s="5" t="s">
         <v>108</v>
       </c>
       <c r="H67" t="s">
@@ -5793,7 +6198,7 @@
       <c r="F68" t="s">
         <v>117</v>
       </c>
-      <c r="G68" t="s">
+      <c r="G68" s="5" t="s">
         <v>117</v>
       </c>
       <c r="H68" t="s">
@@ -5828,7 +6233,7 @@
       <c r="F69" t="s">
         <v>118</v>
       </c>
-      <c r="G69" t="s">
+      <c r="G69" s="5" t="s">
         <v>118</v>
       </c>
       <c r="H69" t="s">
@@ -5860,7 +6265,7 @@
       <c r="F70" t="s">
         <v>119</v>
       </c>
-      <c r="G70" t="s">
+      <c r="G70" s="5" t="s">
         <v>119</v>
       </c>
       <c r="H70" t="s">
@@ -5895,7 +6300,7 @@
       <c r="F71" t="s">
         <v>120</v>
       </c>
-      <c r="G71" t="s">
+      <c r="G71" s="5" t="s">
         <v>120</v>
       </c>
       <c r="H71" t="s">
@@ -5930,7 +6335,7 @@
       <c r="F72" t="s">
         <v>121</v>
       </c>
-      <c r="G72" t="s">
+      <c r="G72" s="5" t="s">
         <v>121</v>
       </c>
       <c r="H72" t="s">
@@ -5965,7 +6370,7 @@
       <c r="F73" t="s">
         <v>122</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G73" s="5" t="s">
         <v>122</v>
       </c>
       <c r="H73" t="s">
@@ -5997,7 +6402,7 @@
       <c r="F74" t="s">
         <v>123</v>
       </c>
-      <c r="G74" t="s">
+      <c r="G74" s="5" t="s">
         <v>123</v>
       </c>
       <c r="H74" t="s">
@@ -6032,7 +6437,7 @@
       <c r="F75" t="s">
         <v>124</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G75" s="5" t="s">
         <v>124</v>
       </c>
       <c r="H75" t="s">
@@ -6067,7 +6472,7 @@
       <c r="F76" t="s">
         <v>125</v>
       </c>
-      <c r="G76" t="s">
+      <c r="G76" s="5" t="s">
         <v>125</v>
       </c>
       <c r="H76" t="s">
@@ -6099,7 +6504,7 @@
       <c r="F77" t="s">
         <v>126</v>
       </c>
-      <c r="G77" t="s">
+      <c r="G77" s="5" t="s">
         <v>126</v>
       </c>
       <c r="H77" t="s">
@@ -6134,7 +6539,7 @@
       <c r="F78" t="s">
         <v>143</v>
       </c>
-      <c r="G78" t="s">
+      <c r="G78" s="5" t="s">
         <v>143</v>
       </c>
       <c r="H78" t="s">
@@ -6553,7 +6958,7 @@
       <c r="F91" t="s">
         <v>156</v>
       </c>
-      <c r="G91" t="s">
+      <c r="G91" s="5" t="s">
         <v>156</v>
       </c>
       <c r="H91" t="s">
@@ -6652,7 +7057,7 @@
       <c r="F94" t="s">
         <v>165</v>
       </c>
-      <c r="G94" t="s">
+      <c r="G94" s="5" t="s">
         <v>165</v>
       </c>
       <c r="H94" t="s">
@@ -6687,7 +7092,7 @@
       <c r="F95" t="s">
         <v>193</v>
       </c>
-      <c r="G95" t="s">
+      <c r="G95" s="5" t="s">
         <v>193</v>
       </c>
       <c r="H95" t="s">
@@ -7522,7 +7927,7 @@
       <c r="F121" t="s">
         <v>163</v>
       </c>
-      <c r="G121" t="s">
+      <c r="G121" s="5" t="s">
         <v>163</v>
       </c>
       <c r="H121" t="s">
@@ -7554,7 +7959,7 @@
       <c r="F122" t="s">
         <v>232</v>
       </c>
-      <c r="G122" t="s">
+      <c r="G122" s="5" t="s">
         <v>232</v>
       </c>
       <c r="H122" t="s">
@@ -7690,7 +8095,7 @@
       <c r="F127" t="s">
         <v>233</v>
       </c>
-      <c r="G127" t="s">
+      <c r="G127" s="5" t="s">
         <v>233</v>
       </c>
       <c r="H127" t="s">
@@ -7800,7 +8205,7 @@
       <c r="F131" t="s">
         <v>234</v>
       </c>
-      <c r="G131" t="s">
+      <c r="G131" s="5" t="s">
         <v>234</v>
       </c>
       <c r="H131" t="s">
@@ -8430,7 +8835,7 @@
       <c r="F149" t="s">
         <v>297</v>
       </c>
-      <c r="G149" t="s">
+      <c r="G149" s="5" t="s">
         <v>297</v>
       </c>
       <c r="H149" t="s">
@@ -8465,7 +8870,7 @@
       <c r="F150" t="s">
         <v>299</v>
       </c>
-      <c r="G150" t="s">
+      <c r="G150" s="5" t="s">
         <v>299</v>
       </c>
       <c r="H150" t="s">
@@ -8500,7 +8905,7 @@
       <c r="F151" t="s">
         <v>300</v>
       </c>
-      <c r="G151" t="s">
+      <c r="G151" s="5" t="s">
         <v>300</v>
       </c>
       <c r="H151" t="s">
@@ -8538,7 +8943,7 @@
       <c r="F152" t="s">
         <v>301</v>
       </c>
-      <c r="G152" t="s">
+      <c r="G152" s="5" t="s">
         <v>301</v>
       </c>
       <c r="H152" t="s">
@@ -8751,7 +9156,7 @@
       <c r="F158" t="s">
         <v>302</v>
       </c>
-      <c r="G158" t="s">
+      <c r="G158" s="5" t="s">
         <v>302</v>
       </c>
       <c r="H158" t="s">
@@ -9069,7 +9474,7 @@
       <c r="F167" t="s">
         <v>316</v>
       </c>
-      <c r="G167" t="s">
+      <c r="G167" s="5" t="s">
         <v>316</v>
       </c>
       <c r="H167" t="s">
@@ -10159,7 +10564,7 @@
       <c r="F199" t="s">
         <v>369</v>
       </c>
-      <c r="G199" t="s">
+      <c r="G199" s="5" t="s">
         <v>369</v>
       </c>
       <c r="H199" t="s">
@@ -10197,7 +10602,7 @@
       <c r="F200" t="s">
         <v>370</v>
       </c>
-      <c r="G200" t="s">
+      <c r="G200" s="5" t="s">
         <v>370</v>
       </c>
       <c r="H200" t="s">
@@ -10235,7 +10640,7 @@
       <c r="F201" t="s">
         <v>371</v>
       </c>
-      <c r="G201" t="s">
+      <c r="G201" s="5" t="s">
         <v>371</v>
       </c>
       <c r="H201" t="s">
@@ -10273,7 +10678,7 @@
       <c r="F202" t="s">
         <v>372</v>
       </c>
-      <c r="G202" t="s">
+      <c r="G202" s="5" t="s">
         <v>372</v>
       </c>
       <c r="H202" t="s">
@@ -10311,7 +10716,7 @@
       <c r="F203" t="s">
         <v>373</v>
       </c>
-      <c r="G203" t="s">
+      <c r="G203" s="5" t="s">
         <v>373</v>
       </c>
       <c r="H203" t="s">
@@ -10349,7 +10754,7 @@
       <c r="F204" t="s">
         <v>374</v>
       </c>
-      <c r="G204" t="s">
+      <c r="G204" s="5" t="s">
         <v>374</v>
       </c>
       <c r="H204" t="s">
@@ -10387,7 +10792,7 @@
       <c r="F205" t="s">
         <v>375</v>
       </c>
-      <c r="G205" t="s">
+      <c r="G205" s="5" t="s">
         <v>375</v>
       </c>
       <c r="H205" t="s">
@@ -10425,7 +10830,7 @@
       <c r="F206" t="s">
         <v>376</v>
       </c>
-      <c r="G206" t="s">
+      <c r="G206" s="5" t="s">
         <v>376</v>
       </c>
       <c r="H206" t="s">
@@ -10463,7 +10868,7 @@
       <c r="F207" t="s">
         <v>377</v>
       </c>
-      <c r="G207" t="s">
+      <c r="G207" s="5" t="s">
         <v>377</v>
       </c>
       <c r="H207" t="s">
@@ -10501,7 +10906,7 @@
       <c r="F208" t="s">
         <v>378</v>
       </c>
-      <c r="G208" t="s">
+      <c r="G208" s="5" t="s">
         <v>378</v>
       </c>
       <c r="H208" t="s">
@@ -10539,7 +10944,7 @@
       <c r="F209" t="s">
         <v>379</v>
       </c>
-      <c r="G209" t="s">
+      <c r="G209" s="5" t="s">
         <v>379</v>
       </c>
       <c r="H209" t="s">
@@ -10577,7 +10982,7 @@
       <c r="F210" t="s">
         <v>380</v>
       </c>
-      <c r="G210" t="s">
+      <c r="G210" s="5" t="s">
         <v>380</v>
       </c>
       <c r="H210" t="s">
@@ -10615,7 +11020,7 @@
       <c r="F211" t="s">
         <v>381</v>
       </c>
-      <c r="G211" t="s">
+      <c r="G211" s="5" t="s">
         <v>381</v>
       </c>
       <c r="H211" t="s">
@@ -10653,7 +11058,7 @@
       <c r="F212" t="s">
         <v>382</v>
       </c>
-      <c r="G212" t="s">
+      <c r="G212" s="5" t="s">
         <v>382</v>
       </c>
       <c r="H212" t="s">
@@ -10691,7 +11096,7 @@
       <c r="F213" t="s">
         <v>411</v>
       </c>
-      <c r="G213" t="s">
+      <c r="G213" s="5" t="s">
         <v>411</v>
       </c>
       <c r="H213" t="s">
@@ -11009,7 +11414,7 @@
       <c r="F222" t="s">
         <v>395</v>
       </c>
-      <c r="G222" t="s">
+      <c r="G222" s="5" t="s">
         <v>395</v>
       </c>
       <c r="H222" t="s">
@@ -11050,7 +11455,7 @@
       <c r="F223" t="s">
         <v>423</v>
       </c>
-      <c r="G223" t="s">
+      <c r="G223" s="5" t="s">
         <v>423</v>
       </c>
       <c r="H223" t="s">
@@ -11500,7 +11905,7 @@
       <c r="F235" t="s">
         <v>463</v>
       </c>
-      <c r="G235" t="s">
+      <c r="G235" s="5" t="s">
         <v>468</v>
       </c>
       <c r="H235" t="s">
@@ -11538,7 +11943,7 @@
       <c r="F236" t="s">
         <v>469</v>
       </c>
-      <c r="G236" t="s">
+      <c r="G236" s="5" t="s">
         <v>469</v>
       </c>
       <c r="H236" t="s">
@@ -11576,7 +11981,7 @@
       <c r="F237" t="s">
         <v>470</v>
       </c>
-      <c r="G237" t="s">
+      <c r="G237" s="5" t="s">
         <v>470</v>
       </c>
       <c r="H237" t="s">
@@ -12198,7 +12603,7 @@
       <c r="F254" t="s">
         <v>518</v>
       </c>
-      <c r="G254" t="s">
+      <c r="G254" s="5" t="s">
         <v>518</v>
       </c>
       <c r="H254" t="s">
@@ -16176,7 +16581,7 @@
       <c r="F371" t="s">
         <v>727</v>
       </c>
-      <c r="G371" t="s">
+      <c r="G371" s="5" t="s">
         <v>517</v>
       </c>
       <c r="H371" t="s">
@@ -16211,7 +16616,7 @@
       <c r="F372" t="s">
         <v>728</v>
       </c>
-      <c r="G372" t="s">
+      <c r="G372" s="5" t="s">
         <v>546</v>
       </c>
       <c r="H372" t="s">
@@ -16653,7 +17058,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="385" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B385" t="s">
         <v>475</v>
       </c>
@@ -16685,7 +17090,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="386" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B386" t="s">
         <v>475</v>
       </c>
@@ -16717,7 +17122,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="387" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B387" t="s">
         <v>475</v>
       </c>
@@ -16749,7 +17154,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="388" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B388" t="s">
         <v>475</v>
       </c>
@@ -16781,7 +17186,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="389" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B389" t="s">
         <v>475</v>
       </c>
@@ -16813,7 +17218,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="390" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B390" t="s">
         <v>475</v>
       </c>
@@ -16844,8 +17249,11 @@
       <c r="N390" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="391" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="O390" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="391" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B391" t="s">
         <v>475</v>
       </c>
@@ -16877,7 +17285,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="392" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B392" t="s">
         <v>475</v>
       </c>
@@ -16909,7 +17317,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="393" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B393" t="s">
         <v>475</v>
       </c>
@@ -16941,7 +17349,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="394" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B394" t="s">
         <v>475</v>
       </c>
@@ -16973,7 +17381,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="395" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B395" t="s">
         <v>475</v>
       </c>
@@ -17005,7 +17413,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="396" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B396" t="s">
         <v>475</v>
       </c>
@@ -17037,7 +17445,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="397" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B397" t="s">
         <v>475</v>
       </c>
@@ -17069,7 +17477,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="398" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B398" t="s">
         <v>475</v>
       </c>
@@ -17101,7 +17509,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="399" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B399" t="s">
         <v>475</v>
       </c>
@@ -17133,7 +17541,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="400" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B400" t="s">
         <v>475</v>
       </c>
@@ -19128,7 +19536,7 @@
       <c r="F467" t="s">
         <v>851</v>
       </c>
-      <c r="G467" t="s">
+      <c r="G467" s="5" t="s">
         <v>851</v>
       </c>
       <c r="H467" t="s">
@@ -19306,7 +19714,7 @@
       <c r="F472" t="s">
         <v>861</v>
       </c>
-      <c r="G472" t="s">
+      <c r="G472" s="5" t="s">
         <v>861</v>
       </c>
       <c r="I472" t="s">
@@ -19341,7 +19749,7 @@
       <c r="F473" t="s">
         <v>865</v>
       </c>
-      <c r="G473" t="s">
+      <c r="G473" s="5" t="s">
         <v>865</v>
       </c>
       <c r="I473" t="s">
@@ -19376,7 +19784,7 @@
       <c r="F474" t="s">
         <v>867</v>
       </c>
-      <c r="G474" t="s">
+      <c r="G474" s="5" t="s">
         <v>867</v>
       </c>
       <c r="H474" t="s">
@@ -19449,7 +19857,7 @@
       <c r="F476" t="s">
         <v>875</v>
       </c>
-      <c r="G476" t="s">
+      <c r="G476" s="5" t="s">
         <v>875</v>
       </c>
       <c r="H476" t="s">
@@ -19490,7 +19898,7 @@
       <c r="F477" t="s">
         <v>878</v>
       </c>
-      <c r="G477" t="s">
+      <c r="G477" s="5" t="s">
         <v>878</v>
       </c>
       <c r="H477" t="s">
@@ -19531,7 +19939,7 @@
       <c r="F478" t="s">
         <v>886</v>
       </c>
-      <c r="G478" t="s">
+      <c r="G478" s="5" t="s">
         <v>886</v>
       </c>
       <c r="H478" t="s">
@@ -19572,7 +19980,7 @@
       <c r="F479" t="s">
         <v>889</v>
       </c>
-      <c r="G479" t="s">
+      <c r="G479" s="5" t="s">
         <v>889</v>
       </c>
       <c r="H479" t="s">
@@ -19610,7 +20018,7 @@
       <c r="F480" t="s">
         <v>897</v>
       </c>
-      <c r="G480" t="s">
+      <c r="G480" s="5" t="s">
         <v>897</v>
       </c>
       <c r="H480" t="s">
@@ -19645,7 +20053,7 @@
       <c r="F481" t="s">
         <v>898</v>
       </c>
-      <c r="G481" t="s">
+      <c r="G481" s="5" t="s">
         <v>898</v>
       </c>
       <c r="H481" t="s">
@@ -19683,7 +20091,7 @@
       <c r="F482" t="s">
         <v>900</v>
       </c>
-      <c r="G482" t="s">
+      <c r="G482" s="5" t="s">
         <v>900</v>
       </c>
       <c r="H482" t="s">
@@ -19721,7 +20129,7 @@
       <c r="F483" t="s">
         <v>905</v>
       </c>
-      <c r="G483" t="s">
+      <c r="G483" s="5" t="s">
         <v>906</v>
       </c>
       <c r="H483" t="s">
@@ -19762,7 +20170,7 @@
       <c r="F484" t="s">
         <v>911</v>
       </c>
-      <c r="G484" t="s">
+      <c r="G484" s="5" t="s">
         <v>911</v>
       </c>
       <c r="H484" t="s">
@@ -19803,7 +20211,7 @@
       <c r="F485" t="s">
         <v>912</v>
       </c>
-      <c r="G485" t="s">
+      <c r="G485" s="5" t="s">
         <v>912</v>
       </c>
       <c r="H485" t="s">
@@ -19844,7 +20252,7 @@
       <c r="F486" t="s">
         <v>913</v>
       </c>
-      <c r="G486" t="s">
+      <c r="G486" s="5" t="s">
         <v>913</v>
       </c>
       <c r="H486" t="s">
@@ -19885,7 +20293,7 @@
       <c r="F487" t="s">
         <v>914</v>
       </c>
-      <c r="G487" t="s">
+      <c r="G487" s="5" t="s">
         <v>914</v>
       </c>
       <c r="H487" t="s">
@@ -19926,7 +20334,7 @@
       <c r="F488" t="s">
         <v>915</v>
       </c>
-      <c r="G488" t="s">
+      <c r="G488" s="5" t="s">
         <v>915</v>
       </c>
       <c r="H488" t="s">
@@ -19964,7 +20372,7 @@
       <c r="F489" t="s">
         <v>929</v>
       </c>
-      <c r="G489" t="s">
+      <c r="G489" s="5" t="s">
         <v>929</v>
       </c>
       <c r="H489" t="s">
@@ -20005,7 +20413,7 @@
       <c r="F490" t="s">
         <v>933</v>
       </c>
-      <c r="G490" t="s">
+      <c r="G490" s="5" t="s">
         <v>933</v>
       </c>
       <c r="H490" t="s">
@@ -20046,7 +20454,7 @@
       <c r="F491" t="s">
         <v>937</v>
       </c>
-      <c r="G491" t="s">
+      <c r="G491" s="5" t="s">
         <v>937</v>
       </c>
       <c r="I491" t="s">
@@ -20081,7 +20489,7 @@
       <c r="F492" t="s">
         <v>942</v>
       </c>
-      <c r="G492" t="s">
+      <c r="G492" s="5" t="s">
         <v>942</v>
       </c>
       <c r="H492" t="s">
@@ -20119,7 +20527,7 @@
       <c r="F493" t="s">
         <v>946</v>
       </c>
-      <c r="G493" t="s">
+      <c r="G493" s="5" t="s">
         <v>946</v>
       </c>
       <c r="H493" t="s">
@@ -20157,7 +20565,7 @@
       <c r="F494" t="s">
         <v>950</v>
       </c>
-      <c r="G494" t="s">
+      <c r="G494" s="5" t="s">
         <v>950</v>
       </c>
       <c r="I494" t="s">
@@ -20192,7 +20600,7 @@
       <c r="F495" t="s">
         <v>954</v>
       </c>
-      <c r="G495" t="s">
+      <c r="G495" s="5" t="s">
         <v>954</v>
       </c>
       <c r="H495" t="s">
@@ -20233,7 +20641,7 @@
       <c r="F496" t="s">
         <v>957</v>
       </c>
-      <c r="G496" t="s">
+      <c r="G496" s="5" t="s">
         <v>957</v>
       </c>
       <c r="I496" t="s">
@@ -20499,7 +20907,7 @@
       <c r="F503" t="s">
         <v>980</v>
       </c>
-      <c r="G503" t="s">
+      <c r="G503" s="5" t="s">
         <v>980</v>
       </c>
       <c r="H503" t="s">
@@ -20839,16 +21247,16 @@
         <v>139</v>
       </c>
       <c r="F512" t="s">
-        <v>1273</v>
-      </c>
-      <c r="G512" t="s">
-        <v>1275</v>
+        <v>1262</v>
+      </c>
+      <c r="G512" s="5" t="s">
+        <v>1264</v>
       </c>
       <c r="I512" t="s">
         <v>837</v>
       </c>
       <c r="J512" t="s">
-        <v>1274</v>
+        <v>1263</v>
       </c>
       <c r="L512" t="s">
         <v>766</v>
@@ -20873,7 +21281,7 @@
       <c r="F513" t="s">
         <v>1010</v>
       </c>
-      <c r="G513" t="s">
+      <c r="G513" s="5" t="s">
         <v>1033</v>
       </c>
       <c r="I513" t="s">
@@ -20905,7 +21313,7 @@
       <c r="F514" t="s">
         <v>1011</v>
       </c>
-      <c r="G514" t="s">
+      <c r="G514" s="5" t="s">
         <v>1034</v>
       </c>
       <c r="I514" t="s">
@@ -20937,7 +21345,7 @@
       <c r="F515" t="s">
         <v>1012</v>
       </c>
-      <c r="G515" t="s">
+      <c r="G515" s="5" t="s">
         <v>1035</v>
       </c>
       <c r="I515" t="s">
@@ -20969,7 +21377,7 @@
       <c r="F516" t="s">
         <v>1013</v>
       </c>
-      <c r="G516" t="s">
+      <c r="G516" s="5" t="s">
         <v>1036</v>
       </c>
       <c r="I516" t="s">
@@ -21001,7 +21409,7 @@
       <c r="F517" t="s">
         <v>1014</v>
       </c>
-      <c r="G517" t="s">
+      <c r="G517" s="5" t="s">
         <v>1037</v>
       </c>
       <c r="I517" t="s">
@@ -21033,7 +21441,7 @@
       <c r="F518" t="s">
         <v>1015</v>
       </c>
-      <c r="G518" t="s">
+      <c r="G518" s="5" t="s">
         <v>1038</v>
       </c>
       <c r="I518" t="s">
@@ -21065,7 +21473,7 @@
       <c r="F519" t="s">
         <v>1016</v>
       </c>
-      <c r="G519" t="s">
+      <c r="G519" s="5" t="s">
         <v>1039</v>
       </c>
       <c r="I519" t="s">
@@ -21097,7 +21505,7 @@
       <c r="F520" t="s">
         <v>1017</v>
       </c>
-      <c r="G520" t="s">
+      <c r="G520" s="5" t="s">
         <v>1040</v>
       </c>
       <c r="I520" t="s">
@@ -21129,7 +21537,7 @@
       <c r="F521" t="s">
         <v>1018</v>
       </c>
-      <c r="G521" t="s">
+      <c r="G521" s="5" t="s">
         <v>1041</v>
       </c>
       <c r="I521" t="s">
@@ -21161,7 +21569,7 @@
       <c r="F522" t="s">
         <v>1019</v>
       </c>
-      <c r="G522" t="s">
+      <c r="G522" s="5" t="s">
         <v>1042</v>
       </c>
       <c r="I522" t="s">
@@ -21193,7 +21601,7 @@
       <c r="F523" t="s">
         <v>1020</v>
       </c>
-      <c r="G523" t="s">
+      <c r="G523" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="I523" t="s">
@@ -21341,7 +21749,7 @@
       <c r="F528" t="s">
         <v>1053</v>
       </c>
-      <c r="G528" t="s">
+      <c r="G528" s="5" t="s">
         <v>1053</v>
       </c>
       <c r="H528" t="s">
@@ -21376,7 +21784,7 @@
       <c r="F529" t="s">
         <v>1054</v>
       </c>
-      <c r="G529" t="s">
+      <c r="G529" s="5" t="s">
         <v>1054</v>
       </c>
       <c r="H529" t="s">
@@ -21411,7 +21819,7 @@
       <c r="F530" t="s">
         <v>1055</v>
       </c>
-      <c r="G530" t="s">
+      <c r="G530" s="5" t="s">
         <v>1055</v>
       </c>
       <c r="H530" t="s">
@@ -21446,7 +21854,7 @@
       <c r="F531" t="s">
         <v>1056</v>
       </c>
-      <c r="G531" t="s">
+      <c r="G531" s="5" t="s">
         <v>1056</v>
       </c>
       <c r="H531" t="s">
@@ -21481,7 +21889,7 @@
       <c r="F532" t="s">
         <v>1057</v>
       </c>
-      <c r="G532" t="s">
+      <c r="G532" s="5" t="s">
         <v>1057</v>
       </c>
       <c r="H532" t="s">
@@ -21516,7 +21924,7 @@
       <c r="F533" t="s">
         <v>1091</v>
       </c>
-      <c r="G533" t="s">
+      <c r="G533" s="5" t="s">
         <v>1092</v>
       </c>
       <c r="H533" t="s">
@@ -21554,7 +21962,7 @@
       <c r="F534" t="s">
         <v>1058</v>
       </c>
-      <c r="G534" t="s">
+      <c r="G534" s="5" t="s">
         <v>1058</v>
       </c>
       <c r="H534" t="s">
@@ -21592,7 +22000,7 @@
       <c r="F535" t="s">
         <v>1059</v>
       </c>
-      <c r="G535" t="s">
+      <c r="G535" s="5" t="s">
         <v>1059</v>
       </c>
       <c r="H535" t="s">
@@ -21627,7 +22035,7 @@
       <c r="F536" t="s">
         <v>1060</v>
       </c>
-      <c r="G536" t="s">
+      <c r="G536" s="5" t="s">
         <v>1060</v>
       </c>
       <c r="H536" t="s">
@@ -21662,7 +22070,7 @@
       <c r="F537" t="s">
         <v>1064</v>
       </c>
-      <c r="G537" t="s">
+      <c r="G537" s="5" t="s">
         <v>1064</v>
       </c>
       <c r="H537" t="s">
@@ -21697,7 +22105,7 @@
       <c r="F538" t="s">
         <v>1061</v>
       </c>
-      <c r="G538" t="s">
+      <c r="G538" s="5" t="s">
         <v>1061</v>
       </c>
       <c r="H538" t="s">
@@ -21732,7 +22140,7 @@
       <c r="F539" t="s">
         <v>1062</v>
       </c>
-      <c r="G539" t="s">
+      <c r="G539" s="5" t="s">
         <v>1062</v>
       </c>
       <c r="H539" t="s">
@@ -21767,7 +22175,7 @@
       <c r="F540" t="s">
         <v>1063</v>
       </c>
-      <c r="G540" t="s">
+      <c r="G540" s="5" t="s">
         <v>1063</v>
       </c>
       <c r="H540" t="s">
@@ -21802,7 +22210,7 @@
       <c r="F541" t="s">
         <v>1065</v>
       </c>
-      <c r="G541" t="s">
+      <c r="G541" s="5" t="s">
         <v>1065</v>
       </c>
       <c r="H541" t="s">
@@ -21837,7 +22245,7 @@
       <c r="F542" t="s">
         <v>1066</v>
       </c>
-      <c r="G542" t="s">
+      <c r="G542" s="5" t="s">
         <v>1066</v>
       </c>
       <c r="H542" t="s">
@@ -21872,7 +22280,7 @@
       <c r="F543" t="s">
         <v>1067</v>
       </c>
-      <c r="G543" t="s">
+      <c r="G543" s="5" t="s">
         <v>1067</v>
       </c>
       <c r="H543" t="s">
@@ -21907,7 +22315,7 @@
       <c r="F544" t="s">
         <v>1098</v>
       </c>
-      <c r="G544" t="s">
+      <c r="G544" s="5" t="s">
         <v>1110</v>
       </c>
       <c r="H544" t="s">
@@ -21942,7 +22350,7 @@
       <c r="F545" t="s">
         <v>1099</v>
       </c>
-      <c r="G545" t="s">
+      <c r="G545" s="5" t="s">
         <v>1111</v>
       </c>
       <c r="H545" t="s">
@@ -21977,7 +22385,7 @@
       <c r="F546" t="s">
         <v>1115</v>
       </c>
-      <c r="G546" t="s">
+      <c r="G546" s="5" t="s">
         <v>1115</v>
       </c>
       <c r="H546" t="s">
@@ -22018,7 +22426,7 @@
       <c r="F547" t="s">
         <v>1100</v>
       </c>
-      <c r="G547" t="s">
+      <c r="G547" s="5" t="s">
         <v>1100</v>
       </c>
       <c r="H547" t="s">
@@ -22056,7 +22464,7 @@
       <c r="F548" t="s">
         <v>1101</v>
       </c>
-      <c r="G548" t="s">
+      <c r="G548" s="5" t="s">
         <v>1101</v>
       </c>
       <c r="H548" t="s">
@@ -22094,7 +22502,7 @@
       <c r="F549" t="s">
         <v>1102</v>
       </c>
-      <c r="G549" t="s">
+      <c r="G549" s="5" t="s">
         <v>1102</v>
       </c>
       <c r="H549" t="s">
@@ -22132,7 +22540,7 @@
       <c r="F550" t="s">
         <v>1103</v>
       </c>
-      <c r="G550" t="s">
+      <c r="G550" s="5" t="s">
         <v>1103</v>
       </c>
       <c r="H550" t="s">
@@ -22170,7 +22578,7 @@
       <c r="F551" t="s">
         <v>1104</v>
       </c>
-      <c r="G551" t="s">
+      <c r="G551" s="5" t="s">
         <v>1104</v>
       </c>
       <c r="H551" t="s">
@@ -22208,7 +22616,7 @@
       <c r="F552" t="s">
         <v>1105</v>
       </c>
-      <c r="G552" t="s">
+      <c r="G552" s="5" t="s">
         <v>1105</v>
       </c>
       <c r="H552" t="s">
@@ -22246,7 +22654,7 @@
       <c r="F553" t="s">
         <v>1106</v>
       </c>
-      <c r="G553" t="s">
+      <c r="G553" s="5" t="s">
         <v>1106</v>
       </c>
       <c r="H553" t="s">
@@ -22281,7 +22689,7 @@
       <c r="F554" t="s">
         <v>1107</v>
       </c>
-      <c r="G554" t="s">
+      <c r="G554" s="5" t="s">
         <v>1107</v>
       </c>
       <c r="H554" t="s">
@@ -22319,7 +22727,7 @@
       <c r="F555" t="s">
         <v>1108</v>
       </c>
-      <c r="G555" t="s">
+      <c r="G555" s="5" t="s">
         <v>1108</v>
       </c>
       <c r="H555" t="s">
@@ -22354,7 +22762,7 @@
       <c r="F556" t="s">
         <v>1109</v>
       </c>
-      <c r="G556" t="s">
+      <c r="G556" s="5" t="s">
         <v>1109</v>
       </c>
       <c r="H556" t="s">
@@ -22506,7 +22914,7 @@
       <c r="F560" t="s">
         <v>1146</v>
       </c>
-      <c r="G560" t="s">
+      <c r="G560" s="5" t="s">
         <v>1146</v>
       </c>
       <c r="H560" t="s">
@@ -22848,7 +23256,7 @@
       <c r="F569" t="s">
         <v>1191</v>
       </c>
-      <c r="G569" t="s">
+      <c r="G569" s="5" t="s">
         <v>1191</v>
       </c>
       <c r="H569" t="s">
@@ -22859,6 +23267,9 @@
       </c>
       <c r="J569" t="s">
         <v>1170</v>
+      </c>
+      <c r="K569" t="s">
+        <v>1325</v>
       </c>
       <c r="L569" t="s">
         <v>766</v>
@@ -22883,7 +23294,7 @@
       <c r="F570" t="s">
         <v>1193</v>
       </c>
-      <c r="G570" t="s">
+      <c r="G570" s="5" t="s">
         <v>1193</v>
       </c>
       <c r="H570" t="s">
@@ -22894,6 +23305,9 @@
       </c>
       <c r="J570" t="s">
         <v>1171</v>
+      </c>
+      <c r="K570" t="s">
+        <v>1327</v>
       </c>
       <c r="L570" t="s">
         <v>766</v>
@@ -22918,7 +23332,7 @@
       <c r="F571" t="s">
         <v>1192</v>
       </c>
-      <c r="G571" t="s">
+      <c r="G571" s="5" t="s">
         <v>1192</v>
       </c>
       <c r="H571" t="s">
@@ -22929,6 +23343,9 @@
       </c>
       <c r="J571" t="s">
         <v>1172</v>
+      </c>
+      <c r="K571" t="s">
+        <v>1329</v>
       </c>
       <c r="L571" t="s">
         <v>766</v>
@@ -22953,7 +23370,7 @@
       <c r="F572" t="s">
         <v>1194</v>
       </c>
-      <c r="G572" t="s">
+      <c r="G572" s="5" t="s">
         <v>1194</v>
       </c>
       <c r="H572" t="s">
@@ -22964,6 +23381,9 @@
       </c>
       <c r="J572" t="s">
         <v>1173</v>
+      </c>
+      <c r="K572" t="s">
+        <v>1328</v>
       </c>
       <c r="L572" t="s">
         <v>766</v>
@@ -22988,7 +23408,7 @@
       <c r="F573" t="s">
         <v>1195</v>
       </c>
-      <c r="G573" t="s">
+      <c r="G573" s="5" t="s">
         <v>1212</v>
       </c>
       <c r="H573" t="s">
@@ -22999,6 +23419,9 @@
       </c>
       <c r="J573" t="s">
         <v>1174</v>
+      </c>
+      <c r="K573" t="s">
+        <v>1326</v>
       </c>
       <c r="L573" t="s">
         <v>766</v>
@@ -23023,7 +23446,7 @@
       <c r="F574" t="s">
         <v>1196</v>
       </c>
-      <c r="G574" t="s">
+      <c r="G574" s="5" t="s">
         <v>1196</v>
       </c>
       <c r="H574" t="s">
@@ -23034,6 +23457,9 @@
       </c>
       <c r="J574" t="s">
         <v>1175</v>
+      </c>
+      <c r="K574" t="s">
+        <v>1330</v>
       </c>
       <c r="L574" t="s">
         <v>766</v>
@@ -23058,7 +23484,7 @@
       <c r="F575" t="s">
         <v>1197</v>
       </c>
-      <c r="G575" t="s">
+      <c r="G575" s="5" t="s">
         <v>1197</v>
       </c>
       <c r="H575" t="s">
@@ -23069,6 +23495,9 @@
       </c>
       <c r="J575" t="s">
         <v>1176</v>
+      </c>
+      <c r="K575" t="s">
+        <v>1331</v>
       </c>
       <c r="L575" t="s">
         <v>766</v>
@@ -23093,7 +23522,7 @@
       <c r="F576" t="s">
         <v>1198</v>
       </c>
-      <c r="G576" t="s">
+      <c r="G576" s="5" t="s">
         <v>1198</v>
       </c>
       <c r="H576" t="s">
@@ -23104,6 +23533,9 @@
       </c>
       <c r="J576" t="s">
         <v>1179</v>
+      </c>
+      <c r="K576" t="s">
+        <v>1332</v>
       </c>
       <c r="L576" t="s">
         <v>766</v>
@@ -23128,7 +23560,7 @@
       <c r="F577" t="s">
         <v>1199</v>
       </c>
-      <c r="G577" t="s">
+      <c r="G577" s="5" t="s">
         <v>1199</v>
       </c>
       <c r="H577" t="s">
@@ -23139,6 +23571,9 @@
       </c>
       <c r="J577" t="s">
         <v>1177</v>
+      </c>
+      <c r="K577" t="s">
+        <v>1333</v>
       </c>
       <c r="L577" t="s">
         <v>766</v>
@@ -23163,7 +23598,7 @@
       <c r="F578" t="s">
         <v>1200</v>
       </c>
-      <c r="G578" t="s">
+      <c r="G578" s="5" t="s">
         <v>1200</v>
       </c>
       <c r="H578" t="s">
@@ -23174,6 +23609,9 @@
       </c>
       <c r="J578" t="s">
         <v>1178</v>
+      </c>
+      <c r="K578" t="s">
+        <v>1334</v>
       </c>
       <c r="L578" t="s">
         <v>766</v>
@@ -23198,7 +23636,7 @@
       <c r="F579" t="s">
         <v>1201</v>
       </c>
-      <c r="G579" t="s">
+      <c r="G579" s="5" t="s">
         <v>1201</v>
       </c>
       <c r="H579" t="s">
@@ -23209,6 +23647,9 @@
       </c>
       <c r="J579" t="s">
         <v>1180</v>
+      </c>
+      <c r="K579" t="s">
+        <v>1335</v>
       </c>
       <c r="L579" t="s">
         <v>766</v>
@@ -23233,7 +23674,7 @@
       <c r="F580" t="s">
         <v>1202</v>
       </c>
-      <c r="G580" t="s">
+      <c r="G580" s="5" t="s">
         <v>1202</v>
       </c>
       <c r="H580" t="s">
@@ -23244,6 +23685,9 @@
       </c>
       <c r="J580" t="s">
         <v>1181</v>
+      </c>
+      <c r="K580" t="s">
+        <v>1336</v>
       </c>
       <c r="L580" t="s">
         <v>766</v>
@@ -23268,7 +23712,7 @@
       <c r="F581" t="s">
         <v>1203</v>
       </c>
-      <c r="G581" t="s">
+      <c r="G581" s="5" t="s">
         <v>1203</v>
       </c>
       <c r="H581" t="s">
@@ -23279,6 +23723,9 @@
       </c>
       <c r="J581" t="s">
         <v>1182</v>
+      </c>
+      <c r="K581" t="s">
+        <v>1337</v>
       </c>
       <c r="L581" t="s">
         <v>766</v>
@@ -23303,7 +23750,7 @@
       <c r="F582" t="s">
         <v>1204</v>
       </c>
-      <c r="G582" t="s">
+      <c r="G582" s="5" t="s">
         <v>1204</v>
       </c>
       <c r="H582" t="s">
@@ -23314,6 +23761,9 @@
       </c>
       <c r="J582" t="s">
         <v>1183</v>
+      </c>
+      <c r="K582" t="s">
+        <v>1338</v>
       </c>
       <c r="L582" t="s">
         <v>766</v>
@@ -23338,7 +23788,7 @@
       <c r="F583" t="s">
         <v>1205</v>
       </c>
-      <c r="G583" t="s">
+      <c r="G583" s="5" t="s">
         <v>1205</v>
       </c>
       <c r="H583" t="s">
@@ -23349,6 +23799,9 @@
       </c>
       <c r="J583" t="s">
         <v>1184</v>
+      </c>
+      <c r="K583" t="s">
+        <v>1339</v>
       </c>
       <c r="L583" t="s">
         <v>766</v>
@@ -23373,7 +23826,7 @@
       <c r="F584" t="s">
         <v>1206</v>
       </c>
-      <c r="G584" t="s">
+      <c r="G584" s="5" t="s">
         <v>1206</v>
       </c>
       <c r="H584" t="s">
@@ -23384,6 +23837,9 @@
       </c>
       <c r="J584" t="s">
         <v>1185</v>
+      </c>
+      <c r="K584" t="s">
+        <v>1340</v>
       </c>
       <c r="L584" t="s">
         <v>766</v>
@@ -23408,7 +23864,7 @@
       <c r="F585" t="s">
         <v>1207</v>
       </c>
-      <c r="G585" t="s">
+      <c r="G585" s="5" t="s">
         <v>1207</v>
       </c>
       <c r="H585" t="s">
@@ -23419,6 +23875,9 @@
       </c>
       <c r="J585" t="s">
         <v>1186</v>
+      </c>
+      <c r="K585" t="s">
+        <v>1341</v>
       </c>
       <c r="L585" t="s">
         <v>766</v>
@@ -23443,7 +23902,7 @@
       <c r="F586" t="s">
         <v>1208</v>
       </c>
-      <c r="G586" t="s">
+      <c r="G586" s="5" t="s">
         <v>1208</v>
       </c>
       <c r="H586" t="s">
@@ -23454,6 +23913,9 @@
       </c>
       <c r="J586" t="s">
         <v>1187</v>
+      </c>
+      <c r="K586" t="s">
+        <v>1342</v>
       </c>
       <c r="L586" t="s">
         <v>766</v>
@@ -23476,10 +23938,10 @@
         <v>139</v>
       </c>
       <c r="F587" t="s">
-        <v>1271</v>
-      </c>
-      <c r="G587" t="s">
-        <v>1271</v>
+        <v>1260</v>
+      </c>
+      <c r="G587" s="5" t="s">
+        <v>1260</v>
       </c>
       <c r="H587" t="s">
         <v>1079</v>
@@ -23488,7 +23950,10 @@
         <v>485</v>
       </c>
       <c r="J587" t="s">
-        <v>1272</v>
+        <v>1261</v>
+      </c>
+      <c r="K587" t="s">
+        <v>1343</v>
       </c>
       <c r="L587" t="s">
         <v>766</v>
@@ -23513,7 +23978,7 @@
       <c r="F588" t="s">
         <v>1209</v>
       </c>
-      <c r="G588" t="s">
+      <c r="G588" s="5" t="s">
         <v>1209</v>
       </c>
       <c r="H588" t="s">
@@ -23524,6 +23989,9 @@
       </c>
       <c r="J588" t="s">
         <v>1188</v>
+      </c>
+      <c r="K588" t="s">
+        <v>1344</v>
       </c>
       <c r="L588" t="s">
         <v>766</v>
@@ -23548,7 +24016,7 @@
       <c r="F589" t="s">
         <v>1210</v>
       </c>
-      <c r="G589" t="s">
+      <c r="G589" s="5" t="s">
         <v>1210</v>
       </c>
       <c r="H589" t="s">
@@ -23559,6 +24027,9 @@
       </c>
       <c r="J589" t="s">
         <v>1189</v>
+      </c>
+      <c r="K589" t="s">
+        <v>1345</v>
       </c>
       <c r="L589" t="s">
         <v>766</v>
@@ -23583,7 +24054,7 @@
       <c r="F590" t="s">
         <v>1211</v>
       </c>
-      <c r="G590" t="s">
+      <c r="G590" s="5" t="s">
         <v>1211</v>
       </c>
       <c r="H590" t="s">
@@ -23594,6 +24065,9 @@
       </c>
       <c r="J590" t="s">
         <v>1190</v>
+      </c>
+      <c r="K590" t="s">
+        <v>1346</v>
       </c>
       <c r="L590" t="s">
         <v>766</v>
@@ -23618,11 +24092,11 @@
       <c r="F591" t="s">
         <v>1232</v>
       </c>
-      <c r="G591" t="s">
-        <v>1265</v>
+      <c r="G591" s="5" t="s">
+        <v>1254</v>
       </c>
       <c r="H591" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I591" t="s">
         <v>837</v>
@@ -23645,7 +24119,7 @@
         <v>461</v>
       </c>
       <c r="C592" t="s">
-        <v>1267</v>
+        <v>1256</v>
       </c>
       <c r="E592" t="s">
         <v>139</v>
@@ -23653,11 +24127,11 @@
       <c r="F592" t="s">
         <v>1233</v>
       </c>
-      <c r="G592" t="s">
-        <v>1249</v>
+      <c r="G592" s="5" t="s">
+        <v>1238</v>
       </c>
       <c r="H592" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I592" t="s">
         <v>837</v>
@@ -23688,11 +24162,11 @@
       <c r="F593" t="s">
         <v>1234</v>
       </c>
-      <c r="G593" t="s">
-        <v>1250</v>
+      <c r="G593" s="5" t="s">
+        <v>1239</v>
       </c>
       <c r="H593" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I593" t="s">
         <v>837</v>
@@ -23715,7 +24189,7 @@
         <v>461</v>
       </c>
       <c r="C594" t="s">
-        <v>1268</v>
+        <v>1257</v>
       </c>
       <c r="E594" t="s">
         <v>139</v>
@@ -23723,11 +24197,11 @@
       <c r="F594" t="s">
         <v>1235</v>
       </c>
-      <c r="G594" t="s">
-        <v>1251</v>
+      <c r="G594" s="5" t="s">
+        <v>1240</v>
       </c>
       <c r="H594" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I594" t="s">
         <v>837</v>
@@ -23750,7 +24224,7 @@
         <v>461</v>
       </c>
       <c r="C595" t="s">
-        <v>1269</v>
+        <v>1258</v>
       </c>
       <c r="E595" t="s">
         <v>139</v>
@@ -23758,11 +24232,11 @@
       <c r="F595" t="s">
         <v>1236</v>
       </c>
-      <c r="G595" t="s">
-        <v>1252</v>
+      <c r="G595" s="5" t="s">
+        <v>1241</v>
       </c>
       <c r="H595" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I595" t="s">
         <v>837</v>
@@ -23785,7 +24259,7 @@
         <v>461</v>
       </c>
       <c r="C596" t="s">
-        <v>1270</v>
+        <v>1259</v>
       </c>
       <c r="E596" t="s">
         <v>139</v>
@@ -23793,11 +24267,11 @@
       <c r="F596" t="s">
         <v>1237</v>
       </c>
-      <c r="G596" t="s">
-        <v>1253</v>
+      <c r="G596" s="5" t="s">
+        <v>1242</v>
       </c>
       <c r="H596" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I596" t="s">
         <v>837</v>
@@ -23826,13 +24300,13 @@
         <v>139</v>
       </c>
       <c r="F597" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G597" t="s">
-        <v>1254</v>
+        <v>1398</v>
+      </c>
+      <c r="G597" s="5" t="s">
+        <v>1243</v>
       </c>
       <c r="H597" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I597" t="s">
         <v>837</v>
@@ -23861,13 +24335,13 @@
         <v>139</v>
       </c>
       <c r="F598" t="s">
-        <v>1239</v>
-      </c>
-      <c r="G598" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G598" s="5" t="s">
+        <v>1244</v>
+      </c>
+      <c r="H598" t="s">
         <v>1255</v>
-      </c>
-      <c r="H598" t="s">
-        <v>1266</v>
       </c>
       <c r="I598" t="s">
         <v>837</v>
@@ -23896,13 +24370,13 @@
         <v>139</v>
       </c>
       <c r="F599" t="s">
-        <v>1240</v>
-      </c>
-      <c r="G599" t="s">
-        <v>1256</v>
+        <v>1400</v>
+      </c>
+      <c r="G599" s="5" t="s">
+        <v>1245</v>
       </c>
       <c r="H599" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I599" t="s">
         <v>837</v>
@@ -23931,13 +24405,13 @@
         <v>139</v>
       </c>
       <c r="F600" t="s">
-        <v>1241</v>
-      </c>
-      <c r="G600" t="s">
-        <v>1257</v>
+        <v>1401</v>
+      </c>
+      <c r="G600" s="5" t="s">
+        <v>1246</v>
       </c>
       <c r="H600" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I600" t="s">
         <v>837</v>
@@ -23966,13 +24440,13 @@
         <v>139</v>
       </c>
       <c r="F601" t="s">
-        <v>1242</v>
-      </c>
-      <c r="G601" t="s">
-        <v>1258</v>
+        <v>1402</v>
+      </c>
+      <c r="G601" s="5" t="s">
+        <v>1247</v>
       </c>
       <c r="H601" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I601" t="s">
         <v>837</v>
@@ -24001,13 +24475,13 @@
         <v>139</v>
       </c>
       <c r="F602" t="s">
-        <v>1243</v>
-      </c>
-      <c r="G602" t="s">
-        <v>1259</v>
+        <v>1403</v>
+      </c>
+      <c r="G602" s="5" t="s">
+        <v>1248</v>
       </c>
       <c r="H602" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I602" t="s">
         <v>837</v>
@@ -24036,13 +24510,13 @@
         <v>139</v>
       </c>
       <c r="F603" t="s">
-        <v>1244</v>
-      </c>
-      <c r="G603" t="s">
-        <v>1260</v>
+        <v>1404</v>
+      </c>
+      <c r="G603" s="5" t="s">
+        <v>1249</v>
       </c>
       <c r="H603" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I603" t="s">
         <v>837</v>
@@ -24071,13 +24545,13 @@
         <v>139</v>
       </c>
       <c r="F604" t="s">
-        <v>1245</v>
-      </c>
-      <c r="G604" t="s">
-        <v>1261</v>
+        <v>1405</v>
+      </c>
+      <c r="G604" s="5" t="s">
+        <v>1250</v>
       </c>
       <c r="H604" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I604" t="s">
         <v>837</v>
@@ -24106,13 +24580,13 @@
         <v>139</v>
       </c>
       <c r="F605" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G605" t="s">
-        <v>1262</v>
+        <v>1406</v>
+      </c>
+      <c r="G605" s="5" t="s">
+        <v>1251</v>
       </c>
       <c r="H605" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I605" t="s">
         <v>837</v>
@@ -24141,13 +24615,13 @@
         <v>139</v>
       </c>
       <c r="F606" t="s">
-        <v>1247</v>
-      </c>
-      <c r="G606" t="s">
-        <v>1263</v>
+        <v>1407</v>
+      </c>
+      <c r="G606" s="5" t="s">
+        <v>1252</v>
       </c>
       <c r="H606" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I606" t="s">
         <v>837</v>
@@ -24176,13 +24650,13 @@
         <v>139</v>
       </c>
       <c r="F607" t="s">
-        <v>1248</v>
-      </c>
-      <c r="G607" t="s">
-        <v>1264</v>
+        <v>1408</v>
+      </c>
+      <c r="G607" s="5" t="s">
+        <v>1253</v>
       </c>
       <c r="H607" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="I607" t="s">
         <v>837</v>
@@ -24197,11 +24671,1398 @@
         <v>401</v>
       </c>
       <c r="N607" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="608" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B608" t="s">
+        <v>461</v>
+      </c>
+      <c r="C608" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E608" t="s">
+        <v>139</v>
+      </c>
+      <c r="F608" t="s">
+        <v>1267</v>
+      </c>
+      <c r="G608" s="5" t="s">
+        <v>1267</v>
+      </c>
+      <c r="H608" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I608" t="s">
+        <v>144</v>
+      </c>
+      <c r="J608" t="s">
+        <v>1324</v>
+      </c>
+      <c r="L608" t="s">
+        <v>766</v>
+      </c>
+      <c r="M608" t="s">
+        <v>401</v>
+      </c>
+      <c r="N608" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="609" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B609" t="s">
+        <v>461</v>
+      </c>
+      <c r="C609" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E609" t="s">
+        <v>139</v>
+      </c>
+      <c r="F609" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G609" s="5" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H609" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I609" t="s">
+        <v>144</v>
+      </c>
+      <c r="J609" t="s">
+        <v>1269</v>
+      </c>
+      <c r="L609" t="s">
+        <v>766</v>
+      </c>
+      <c r="M609" t="s">
+        <v>401</v>
+      </c>
+      <c r="N609" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="610" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B610" t="s">
+        <v>461</v>
+      </c>
+      <c r="C610" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E610" t="s">
+        <v>139</v>
+      </c>
+      <c r="F610" t="s">
+        <v>1270</v>
+      </c>
+      <c r="G610" s="5" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H610" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I610" t="s">
+        <v>144</v>
+      </c>
+      <c r="J610" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L610" t="s">
+        <v>766</v>
+      </c>
+      <c r="M610" t="s">
+        <v>401</v>
+      </c>
+      <c r="N610" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="611" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B611" t="s">
+        <v>461</v>
+      </c>
+      <c r="C611" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E611" t="s">
+        <v>139</v>
+      </c>
+      <c r="F611" t="s">
+        <v>1272</v>
+      </c>
+      <c r="G611" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H611" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I611" t="s">
+        <v>144</v>
+      </c>
+      <c r="J611" t="s">
+        <v>1273</v>
+      </c>
+      <c r="L611" t="s">
+        <v>766</v>
+      </c>
+      <c r="M611" t="s">
+        <v>401</v>
+      </c>
+      <c r="N611" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="612" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B612" t="s">
+        <v>461</v>
+      </c>
+      <c r="C612" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D612" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E612" t="s">
+        <v>139</v>
+      </c>
+      <c r="F612" t="s">
+        <v>1275</v>
+      </c>
+      <c r="G612" s="5" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H612" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I612" t="s">
+        <v>144</v>
+      </c>
+      <c r="J612" t="s">
+        <v>1276</v>
+      </c>
+      <c r="L612" t="s">
+        <v>766</v>
+      </c>
+      <c r="M612" t="s">
+        <v>401</v>
+      </c>
+      <c r="N612" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="613" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B613" t="s">
+        <v>461</v>
+      </c>
+      <c r="C613" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D613" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E613" t="s">
+        <v>139</v>
+      </c>
+      <c r="F613" t="s">
+        <v>1278</v>
+      </c>
+      <c r="G613" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H613" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I613" t="s">
+        <v>144</v>
+      </c>
+      <c r="J613" t="s">
+        <v>1279</v>
+      </c>
+      <c r="L613" t="s">
+        <v>766</v>
+      </c>
+      <c r="M613" t="s">
+        <v>401</v>
+      </c>
+      <c r="N613" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="614" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B614" t="s">
+        <v>461</v>
+      </c>
+      <c r="C614" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D614" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E614" t="s">
+        <v>139</v>
+      </c>
+      <c r="F614" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G614" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="H614" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I614" t="s">
+        <v>144</v>
+      </c>
+      <c r="J614" t="s">
+        <v>1282</v>
+      </c>
+      <c r="L614" t="s">
+        <v>766</v>
+      </c>
+      <c r="M614" t="s">
+        <v>401</v>
+      </c>
+      <c r="N614" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="615" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B615" t="s">
+        <v>461</v>
+      </c>
+      <c r="C615" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D615" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E615" t="s">
+        <v>139</v>
+      </c>
+      <c r="F615" t="s">
+        <v>1284</v>
+      </c>
+      <c r="G615" s="5" t="s">
+        <v>1284</v>
+      </c>
+      <c r="H615" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I615" t="s">
+        <v>144</v>
+      </c>
+      <c r="J615" t="s">
+        <v>1285</v>
+      </c>
+      <c r="L615" t="s">
+        <v>766</v>
+      </c>
+      <c r="M615" t="s">
+        <v>401</v>
+      </c>
+      <c r="N615" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="616" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B616" t="s">
+        <v>461</v>
+      </c>
+      <c r="C616" t="s">
+        <v>484</v>
+      </c>
+      <c r="D616" t="s">
+        <v>484</v>
+      </c>
+      <c r="E616" t="s">
+        <v>139</v>
+      </c>
+      <c r="F616" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G616" s="5" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H616" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I616" t="s">
+        <v>144</v>
+      </c>
+      <c r="J616" t="s">
+        <v>1287</v>
+      </c>
+      <c r="L616" t="s">
+        <v>766</v>
+      </c>
+      <c r="M616" t="s">
+        <v>401</v>
+      </c>
+      <c r="N616" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="617" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B617" t="s">
+        <v>461</v>
+      </c>
+      <c r="C617" t="s">
+        <v>449</v>
+      </c>
+      <c r="D617" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E617" t="s">
+        <v>139</v>
+      </c>
+      <c r="F617" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G617" s="5" t="s">
+        <v>1289</v>
+      </c>
+      <c r="H617" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I617" t="s">
+        <v>144</v>
+      </c>
+      <c r="J617" t="s">
+        <v>1290</v>
+      </c>
+      <c r="L617" t="s">
+        <v>766</v>
+      </c>
+      <c r="M617" t="s">
+        <v>401</v>
+      </c>
+      <c r="N617" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="618" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B618" t="s">
+        <v>461</v>
+      </c>
+      <c r="C618" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D618" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E618" t="s">
+        <v>139</v>
+      </c>
+      <c r="F618" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G618" s="5" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H618" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I618" t="s">
+        <v>144</v>
+      </c>
+      <c r="J618" t="s">
+        <v>1293</v>
+      </c>
+      <c r="L618" t="s">
+        <v>766</v>
+      </c>
+      <c r="M618" t="s">
+        <v>401</v>
+      </c>
+      <c r="N618" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="619" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B619" t="s">
+        <v>461</v>
+      </c>
+      <c r="C619" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D619" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E619" t="s">
+        <v>139</v>
+      </c>
+      <c r="F619" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G619" s="5" t="s">
+        <v>1295</v>
+      </c>
+      <c r="H619" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I619" t="s">
+        <v>144</v>
+      </c>
+      <c r="J619" t="s">
+        <v>1296</v>
+      </c>
+      <c r="L619" t="s">
+        <v>766</v>
+      </c>
+      <c r="M619" t="s">
+        <v>401</v>
+      </c>
+      <c r="N619" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="620" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B620" t="s">
+        <v>461</v>
+      </c>
+      <c r="C620" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D620" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E620" t="s">
+        <v>139</v>
+      </c>
+      <c r="F620" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G620" s="5" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H620" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I620" t="s">
+        <v>144</v>
+      </c>
+      <c r="J620" t="s">
+        <v>1299</v>
+      </c>
+      <c r="L620" t="s">
+        <v>766</v>
+      </c>
+      <c r="M620" t="s">
+        <v>401</v>
+      </c>
+      <c r="N620" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="621" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B621" t="s">
+        <v>461</v>
+      </c>
+      <c r="C621" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D621" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E621" t="s">
+        <v>139</v>
+      </c>
+      <c r="F621" t="s">
+        <v>1301</v>
+      </c>
+      <c r="G621" s="5" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H621" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I621" t="s">
+        <v>144</v>
+      </c>
+      <c r="J621" t="s">
+        <v>1302</v>
+      </c>
+      <c r="L621" t="s">
+        <v>766</v>
+      </c>
+      <c r="M621" t="s">
+        <v>401</v>
+      </c>
+      <c r="N621" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="622" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B622" t="s">
+        <v>461</v>
+      </c>
+      <c r="C622" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D622" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E622" t="s">
+        <v>139</v>
+      </c>
+      <c r="F622" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G622" s="5" t="s">
+        <v>1304</v>
+      </c>
+      <c r="H622" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I622" t="s">
+        <v>144</v>
+      </c>
+      <c r="J622" t="s">
+        <v>1305</v>
+      </c>
+      <c r="L622" t="s">
+        <v>766</v>
+      </c>
+      <c r="M622" t="s">
+        <v>401</v>
+      </c>
+      <c r="N622" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="623" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B623" t="s">
+        <v>461</v>
+      </c>
+      <c r="C623" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D623" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E623" t="s">
+        <v>139</v>
+      </c>
+      <c r="F623" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G623" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H623" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I623" t="s">
+        <v>144</v>
+      </c>
+      <c r="J623" t="s">
+        <v>1308</v>
+      </c>
+      <c r="L623" t="s">
+        <v>766</v>
+      </c>
+      <c r="M623" t="s">
+        <v>401</v>
+      </c>
+      <c r="N623" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="624" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B624" t="s">
+        <v>461</v>
+      </c>
+      <c r="C624" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D624" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E624" t="s">
+        <v>139</v>
+      </c>
+      <c r="F624" t="s">
+        <v>1310</v>
+      </c>
+      <c r="G624" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="H624" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I624" t="s">
+        <v>144</v>
+      </c>
+      <c r="J624" t="s">
+        <v>1311</v>
+      </c>
+      <c r="L624" t="s">
+        <v>766</v>
+      </c>
+      <c r="M624" t="s">
+        <v>401</v>
+      </c>
+      <c r="N624" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="625" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B625" t="s">
+        <v>461</v>
+      </c>
+      <c r="C625" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D625" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E625" t="s">
+        <v>139</v>
+      </c>
+      <c r="F625" t="s">
+        <v>1313</v>
+      </c>
+      <c r="G625" s="5" t="s">
+        <v>1313</v>
+      </c>
+      <c r="H625" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I625" t="s">
+        <v>144</v>
+      </c>
+      <c r="J625" t="s">
+        <v>1314</v>
+      </c>
+      <c r="L625" t="s">
+        <v>766</v>
+      </c>
+      <c r="M625" t="s">
+        <v>401</v>
+      </c>
+      <c r="N625" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="626" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B626" t="s">
+        <v>461</v>
+      </c>
+      <c r="C626" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D626" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E626" t="s">
+        <v>139</v>
+      </c>
+      <c r="F626" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G626" s="5" t="s">
+        <v>1316</v>
+      </c>
+      <c r="H626" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I626" t="s">
+        <v>144</v>
+      </c>
+      <c r="J626" t="s">
+        <v>1317</v>
+      </c>
+      <c r="L626" t="s">
+        <v>766</v>
+      </c>
+      <c r="M626" t="s">
+        <v>401</v>
+      </c>
+      <c r="N626" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="627" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B627" t="s">
+        <v>461</v>
+      </c>
+      <c r="C627" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D627" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E627" t="s">
+        <v>139</v>
+      </c>
+      <c r="F627" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G627" s="5" t="s">
+        <v>1319</v>
+      </c>
+      <c r="H627" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I627" t="s">
+        <v>144</v>
+      </c>
+      <c r="J627" t="s">
+        <v>1320</v>
+      </c>
+      <c r="L627" t="s">
+        <v>766</v>
+      </c>
+      <c r="M627" t="s">
+        <v>401</v>
+      </c>
+      <c r="N627" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="628" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B628" t="s">
+        <v>461</v>
+      </c>
+      <c r="C628" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D628" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E628" t="s">
+        <v>139</v>
+      </c>
+      <c r="F628" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G628" s="5" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H628" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I628" t="s">
+        <v>144</v>
+      </c>
+      <c r="J628" t="s">
+        <v>1323</v>
+      </c>
+      <c r="L628" t="s">
+        <v>766</v>
+      </c>
+      <c r="M628" t="s">
+        <v>401</v>
+      </c>
+      <c r="N628" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="629" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B629" t="s">
+        <v>461</v>
+      </c>
+      <c r="C629" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E629" t="s">
+        <v>139</v>
+      </c>
+      <c r="F629" t="s">
+        <v>1369</v>
+      </c>
+      <c r="G629" s="5" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H629" t="s">
+        <v>520</v>
+      </c>
+      <c r="I629" t="s">
+        <v>298</v>
+      </c>
+      <c r="J629" t="s">
+        <v>1347</v>
+      </c>
+      <c r="L629" t="s">
+        <v>766</v>
+      </c>
+      <c r="M629" t="s">
+        <v>401</v>
+      </c>
+      <c r="N629" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="630" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B630" t="s">
+        <v>461</v>
+      </c>
+      <c r="C630" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E630" t="s">
+        <v>139</v>
+      </c>
+      <c r="F630" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G630" s="5" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H630" t="s">
+        <v>1348</v>
+      </c>
+      <c r="I630" t="s">
+        <v>298</v>
+      </c>
+      <c r="J630" t="s">
+        <v>1349</v>
+      </c>
+      <c r="L630" t="s">
+        <v>766</v>
+      </c>
+      <c r="M630" t="s">
+        <v>401</v>
+      </c>
+      <c r="N630" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="631" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B631" t="s">
+        <v>461</v>
+      </c>
+      <c r="C631" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E631" t="s">
+        <v>139</v>
+      </c>
+      <c r="F631" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G631" s="5" t="s">
+        <v>1385</v>
+      </c>
+      <c r="H631" t="s">
+        <v>1348</v>
+      </c>
+      <c r="I631" t="s">
+        <v>298</v>
+      </c>
+      <c r="J631" t="s">
+        <v>1350</v>
+      </c>
+      <c r="L631" t="s">
+        <v>766</v>
+      </c>
+      <c r="M631" t="s">
+        <v>401</v>
+      </c>
+      <c r="N631" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="632" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B632" t="s">
+        <v>461</v>
+      </c>
+      <c r="C632" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E632" t="s">
+        <v>139</v>
+      </c>
+      <c r="F632" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G632" s="5" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H632" t="s">
+        <v>520</v>
+      </c>
+      <c r="I632" t="s">
+        <v>298</v>
+      </c>
+      <c r="J632" t="s">
+        <v>1357</v>
+      </c>
+      <c r="L632" t="s">
+        <v>766</v>
+      </c>
+      <c r="M632" t="s">
+        <v>401</v>
+      </c>
+      <c r="N632" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="633" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B633" t="s">
+        <v>461</v>
+      </c>
+      <c r="C633" t="s">
+        <v>449</v>
+      </c>
+      <c r="E633" t="s">
+        <v>139</v>
+      </c>
+      <c r="F633" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G633" s="5" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H633" t="s">
+        <v>520</v>
+      </c>
+      <c r="I633" t="s">
+        <v>298</v>
+      </c>
+      <c r="J633" t="s">
+        <v>1358</v>
+      </c>
+      <c r="L633" t="s">
+        <v>766</v>
+      </c>
+      <c r="M633" t="s">
+        <v>401</v>
+      </c>
+      <c r="N633" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="634" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B634" t="s">
+        <v>461</v>
+      </c>
+      <c r="C634" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E634" t="s">
+        <v>139</v>
+      </c>
+      <c r="F634" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G634" s="5" t="s">
+        <v>1388</v>
+      </c>
+      <c r="H634" t="s">
+        <v>520</v>
+      </c>
+      <c r="I634" t="s">
+        <v>298</v>
+      </c>
+      <c r="J634" t="s">
+        <v>1359</v>
+      </c>
+      <c r="L634" t="s">
+        <v>766</v>
+      </c>
+      <c r="M634" t="s">
+        <v>401</v>
+      </c>
+      <c r="N634" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="635" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B635" t="s">
+        <v>461</v>
+      </c>
+      <c r="C635" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E635" t="s">
+        <v>139</v>
+      </c>
+      <c r="F635" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G635" s="5" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H635" t="s">
+        <v>520</v>
+      </c>
+      <c r="I635" t="s">
+        <v>298</v>
+      </c>
+      <c r="J635" t="s">
+        <v>1360</v>
+      </c>
+      <c r="L635" t="s">
+        <v>766</v>
+      </c>
+      <c r="M635" t="s">
+        <v>401</v>
+      </c>
+      <c r="N635" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="636" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B636" t="s">
+        <v>461</v>
+      </c>
+      <c r="C636" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E636" t="s">
+        <v>139</v>
+      </c>
+      <c r="F636" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G636" s="5" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H636" t="s">
+        <v>520</v>
+      </c>
+      <c r="I636" t="s">
+        <v>298</v>
+      </c>
+      <c r="J636" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L636" t="s">
+        <v>766</v>
+      </c>
+      <c r="M636" t="s">
+        <v>401</v>
+      </c>
+      <c r="N636" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="637" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B637" t="s">
+        <v>461</v>
+      </c>
+      <c r="C637" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E637" t="s">
+        <v>139</v>
+      </c>
+      <c r="F637" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G637" s="5" t="s">
+        <v>1391</v>
+      </c>
+      <c r="H637" t="s">
+        <v>520</v>
+      </c>
+      <c r="I637" t="s">
+        <v>298</v>
+      </c>
+      <c r="J637" t="s">
+        <v>1362</v>
+      </c>
+      <c r="L637" t="s">
+        <v>766</v>
+      </c>
+      <c r="M637" t="s">
+        <v>401</v>
+      </c>
+      <c r="N637" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="638" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B638" t="s">
+        <v>461</v>
+      </c>
+      <c r="C638" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E638" t="s">
+        <v>139</v>
+      </c>
+      <c r="F638" t="s">
+        <v>1377</v>
+      </c>
+      <c r="G638" s="5" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H638" t="s">
+        <v>520</v>
+      </c>
+      <c r="I638" t="s">
+        <v>298</v>
+      </c>
+      <c r="J638" t="s">
+        <v>1363</v>
+      </c>
+      <c r="L638" t="s">
+        <v>766</v>
+      </c>
+      <c r="M638" t="s">
+        <v>401</v>
+      </c>
+      <c r="N638" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="639" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B639" t="s">
+        <v>461</v>
+      </c>
+      <c r="C639" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E639" t="s">
+        <v>139</v>
+      </c>
+      <c r="F639" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G639" s="5" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H639" t="s">
+        <v>520</v>
+      </c>
+      <c r="I639" t="s">
+        <v>298</v>
+      </c>
+      <c r="J639" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L639" t="s">
+        <v>766</v>
+      </c>
+      <c r="M639" t="s">
+        <v>401</v>
+      </c>
+      <c r="N639" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="640" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B640" t="s">
+        <v>461</v>
+      </c>
+      <c r="C640" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E640" t="s">
+        <v>139</v>
+      </c>
+      <c r="F640" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G640" s="5" t="s">
+        <v>1394</v>
+      </c>
+      <c r="H640" t="s">
+        <v>520</v>
+      </c>
+      <c r="I640" t="s">
+        <v>298</v>
+      </c>
+      <c r="J640" t="s">
+        <v>1365</v>
+      </c>
+      <c r="L640" t="s">
+        <v>766</v>
+      </c>
+      <c r="M640" t="s">
+        <v>401</v>
+      </c>
+      <c r="N640" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="641" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B641" t="s">
+        <v>461</v>
+      </c>
+      <c r="C641" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E641" t="s">
+        <v>139</v>
+      </c>
+      <c r="F641" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G641" s="5" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H641" t="s">
+        <v>520</v>
+      </c>
+      <c r="I641" t="s">
+        <v>298</v>
+      </c>
+      <c r="J641" t="s">
+        <v>1366</v>
+      </c>
+      <c r="L641" t="s">
+        <v>766</v>
+      </c>
+      <c r="M641" t="s">
+        <v>401</v>
+      </c>
+      <c r="N641" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="642" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B642" t="s">
+        <v>461</v>
+      </c>
+      <c r="C642" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E642" t="s">
+        <v>139</v>
+      </c>
+      <c r="F642" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G642" s="5" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H642" t="s">
+        <v>520</v>
+      </c>
+      <c r="I642" t="s">
+        <v>298</v>
+      </c>
+      <c r="J642" t="s">
+        <v>1367</v>
+      </c>
+      <c r="L642" t="s">
+        <v>766</v>
+      </c>
+      <c r="M642" t="s">
+        <v>401</v>
+      </c>
+      <c r="N642" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="643" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B643" t="s">
+        <v>461</v>
+      </c>
+      <c r="C643" t="s">
+        <v>484</v>
+      </c>
+      <c r="E643" t="s">
+        <v>139</v>
+      </c>
+      <c r="F643" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G643" s="5" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H643" t="s">
+        <v>520</v>
+      </c>
+      <c r="I643" t="s">
+        <v>298</v>
+      </c>
+      <c r="J643" t="s">
+        <v>1368</v>
+      </c>
+      <c r="L643" t="s">
+        <v>766</v>
+      </c>
+      <c r="M643" t="s">
+        <v>401</v>
+      </c>
+      <c r="N643" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="644" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B644" t="s">
+        <v>461</v>
+      </c>
+      <c r="C644" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E644" t="s">
+        <v>139</v>
+      </c>
+      <c r="F644" t="s">
+        <v>1351</v>
+      </c>
+      <c r="G644" s="5" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H644" t="s">
+        <v>1351</v>
+      </c>
+      <c r="I644" t="s">
+        <v>1352</v>
+      </c>
+      <c r="J644" t="s">
+        <v>1353</v>
+      </c>
+      <c r="L644" t="s">
+        <v>766</v>
+      </c>
+      <c r="M644" t="s">
+        <v>401</v>
+      </c>
+      <c r="N644" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="645" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B645" t="s">
+        <v>461</v>
+      </c>
+      <c r="C645" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D645" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E645" t="s">
+        <v>139</v>
+      </c>
+      <c r="F645" t="s">
+        <v>1355</v>
+      </c>
+      <c r="G645" s="5" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H645" t="s">
+        <v>1351</v>
+      </c>
+      <c r="I645" t="s">
+        <v>1352</v>
+      </c>
+      <c r="J645" t="s">
+        <v>1356</v>
+      </c>
+      <c r="L645" t="s">
+        <v>766</v>
+      </c>
+      <c r="M645" t="s">
+        <v>401</v>
+      </c>
+      <c r="N645" t="s">
         <v>1068</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="G629:G631 G632:G643" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>